--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -18,16 +18,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
-    <t>次数</t>
+    <t>监控次数</t>
   </si>
   <si>
-    <t>上传流量</t>
+    <t>上行流量</t>
   </si>
   <si>
-    <t>下载流量</t>
+    <t>下行流量</t>
   </si>
   <si>
-    <t>总计</t>
+    <t>流量总计</t>
   </si>
   <si>
     <t>Pass占百分比</t>
@@ -132,10 +132,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>cpu!$A$2:$A$11</c:f>
+              <c:f>cpu!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -150,60 +150,30 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>cpu!$B$2:$B$11</c:f>
+              <c:f>cpu!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>3.2</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.2</c:v>
+                  <c:v>2.9</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3.2</c:v>
+                  <c:v>2.9</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3.2</c:v>
+                  <c:v>2.9</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>3.2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.2</c:v>
+                  <c:v>2.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -324,17 +294,17 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>上传流量</c:v>
+                  <c:v>上行流量</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$11</c:f>
+              <c:f>netflow!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -349,60 +319,30 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$B$2:$B$11</c:f>
+              <c:f>netflow!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -417,17 +357,17 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>下载流量</c:v>
+                  <c:v>下行流量</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$10</c:f>
+              <c:f>netflow!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -439,57 +379,27 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$C$2:$C$10</c:f>
+              <c:f>netflow!$C$2:$C$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>116028</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -504,17 +414,17 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>总计</c:v>
+                  <c:v>流量总计</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$10</c:f>
+              <c:f>netflow!$A$2:$A$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -526,57 +436,27 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$D$2:$D$10</c:f>
+              <c:f>netflow!$D$2:$D$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>232056</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>232056</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>232056</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>232056</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -704,10 +584,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>men!$A$2:$A$11</c:f>
+              <c:f>men!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -722,60 +602,30 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>7</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>men!$B$2:$B$11</c:f>
+              <c:f>men!$B$2:$B$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>121</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>118</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>115</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>118</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>112</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>118</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>115</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>118</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1250,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1266,7 +1116,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1274,7 +1124,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1282,7 +1132,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1290,7 +1140,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1298,47 +1148,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -1349,7 +1159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1371,13 +1181,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>232056</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1385,13 +1195,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>232056</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1399,13 +1209,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>232056</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1413,13 +1223,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>232056</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1427,83 +1237,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>116028</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
+        <v>232056</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1254,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1530,7 +1270,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1538,7 +1278,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1546,7 +1286,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>115</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1554,7 +1294,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1562,47 +1302,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>118</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -161,19 +161,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.9</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.9</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.9</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2.9</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.9</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -364,10 +364,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$5</c:f>
+              <c:f>netflow!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -379,16 +379,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$C$2:$C$5</c:f>
+              <c:f>netflow!$C$2:$C$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>116028</c:v>
                 </c:pt>
@@ -399,6 +402,9 @@
                   <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>116028</c:v>
                 </c:pt>
               </c:numCache>
@@ -421,10 +427,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$5</c:f>
+              <c:f>netflow!$A$2:$A$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -436,16 +442,19 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$D$2:$D$5</c:f>
+              <c:f>netflow!$D$2:$D$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>232056</c:v>
                 </c:pt>
@@ -456,6 +465,9 @@
                   <c:v>232056</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="4">
                   <c:v>232056</c:v>
                 </c:pt>
               </c:numCache>
@@ -613,19 +625,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>127</c:v>
+                  <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>131</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>128</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>140</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>140</c:v>
+                  <c:v>143</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1116,7 +1128,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1124,7 +1136,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1132,7 +1144,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1140,7 +1152,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1148,7 +1160,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1270,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1278,7 +1290,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1294,7 +1306,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1302,7 +1314,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -132,10 +132,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>cpu!$A$2:$A$6</c:f>
+              <c:f>cpu!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -150,16 +150,31 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>cpu!$B$2:$B$6</c:f>
+              <c:f>cpu!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -173,6 +188,21 @@
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
@@ -301,10 +331,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$6</c:f>
+              <c:f>netflow!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -319,16 +349,31 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$B$2:$B$6</c:f>
+              <c:f>netflow!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>116028</c:v>
                 </c:pt>
@@ -342,6 +387,21 @@
                   <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>116028</c:v>
                 </c:pt>
               </c:numCache>
@@ -364,10 +424,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$6</c:f>
+              <c:f>netflow!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -382,16 +442,31 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$C$2:$C$6</c:f>
+              <c:f>netflow!$C$2:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>116028</c:v>
                 </c:pt>
@@ -405,6 +480,21 @@
                   <c:v>116028</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>116028</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>116028</c:v>
                 </c:pt>
               </c:numCache>
@@ -427,10 +517,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$6</c:f>
+              <c:f>netflow!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -445,16 +535,31 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$D$2:$D$6</c:f>
+              <c:f>netflow!$D$2:$D$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>232056</c:v>
                 </c:pt>
@@ -468,6 +573,21 @@
                   <c:v>232056</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>232056</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>232056</c:v>
                 </c:pt>
               </c:numCache>
@@ -596,10 +716,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>men!$A$2:$A$6</c:f>
+              <c:f>men!$A$2:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -614,29 +734,59 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>men!$B$2:$B$6</c:f>
+              <c:f>men!$B$2:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+                <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>128</c:v>
+                  <c:v>129</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>137</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>128</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>134</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>143</c:v>
                 </c:pt>
               </c:numCache>
@@ -1112,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1160,6 +1310,46 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>3</v>
       </c>
     </row>
@@ -1171,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1255,6 +1445,76 @@
         <v>116028</v>
       </c>
       <c r="D6">
+        <v>232056</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>116028</v>
+      </c>
+      <c r="C7">
+        <v>116028</v>
+      </c>
+      <c r="D7">
+        <v>232056</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>116028</v>
+      </c>
+      <c r="C8">
+        <v>116028</v>
+      </c>
+      <c r="D8">
+        <v>232056</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>116028</v>
+      </c>
+      <c r="C9">
+        <v>116028</v>
+      </c>
+      <c r="D9">
+        <v>232056</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>116028</v>
+      </c>
+      <c r="C10">
+        <v>116028</v>
+      </c>
+      <c r="D10">
+        <v>232056</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>116028</v>
+      </c>
+      <c r="C11">
+        <v>116028</v>
+      </c>
+      <c r="D11">
         <v>232056</v>
       </c>
     </row>
@@ -1266,7 +1526,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1282,7 +1542,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1290,7 +1550,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1298,7 +1558,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1314,6 +1574,46 @@
         <v>5</v>
       </c>
       <c r="B6">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
         <v>143</v>
       </c>
     </row>

--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -10,15 +10,22 @@
     <sheet name="cpu" sheetId="1" r:id="rId1"/>
     <sheet name="netflow" sheetId="2" r:id="rId2"/>
     <sheet name="men" sheetId="3" r:id="rId3"/>
+    <sheet name="batt" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>监控次数</t>
+  </si>
+  <si>
+    <t>cpu占用率%</t>
+  </si>
+  <si>
+    <t>耗电百分比</t>
   </si>
   <si>
     <t>上行流量</t>
@@ -31,9 +38,6 @@
   </si>
   <si>
     <t>Pass占百分比</t>
-  </si>
-  <si>
-    <t>cpu占用率(单位:G)</t>
   </si>
 </sst>
 </file>
@@ -105,7 +109,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>cpu占用率</a:t>
+              <a:t>进程cpu占用率</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -125,17 +129,17 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>cpu占用率(单位:G)</c:v>
+                  <c:v>cpu占用率%</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>cpu!$A$2:$A$11</c:f>
+              <c:f>cpu!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -165,45 +169,345 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>cpu!$B$2:$B$11</c:f>
+              <c:f>cpu!$B$2:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>163</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3</c:v>
+                  <c:v>159</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3</c:v>
+                  <c:v>143</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3</c:v>
+                  <c:v>154</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3</c:v>
+                  <c:v>178</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>3</c:v>
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>156</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>153</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>178</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>157</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>196</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>162</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>168</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>184</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>159</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>159</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -304,7 +608,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>流量统计图</a:t>
+              <a:t>流量统计曲线</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -331,10 +635,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$11</c:f>
+              <c:f>netflow!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -364,45 +668,345 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$B$2:$B$11</c:f>
+              <c:f>netflow!$B$2:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-110393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -424,10 +1028,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$11</c:f>
+              <c:f>netflow!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -457,45 +1061,345 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$C$2:$C$11</c:f>
+              <c:f>netflow!$C$2:$C$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>116028</c:v>
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-110393</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-110393</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -517,10 +1421,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>netflow!$A$2:$A$11</c:f>
+              <c:f>netflow!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -550,45 +1454,345 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>netflow!$D$2:$D$11</c:f>
+              <c:f>netflow!$D$2:$D$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>232056</c:v>
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-220786</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-220786</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -689,7 +1893,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>内存占有率统计图</a:t>
+              <a:t>进程mem占有率</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -716,10 +1920,10 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>men!$A$2:$A$11</c:f>
+              <c:f>men!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -749,45 +1953,345 @@
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>men!$B$2:$B$11</c:f>
+              <c:f>men!$B$2:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>129</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>131</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>131</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>134</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>134</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>134</c:v>
+                  <c:v>12.6</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>128</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>128</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>128</c:v>
+                  <c:v>12.1</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>143</c:v>
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.1</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -844,7 +2348,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-US"/>
-                  <a:t>pass值：k</a:t>
+                  <a:t>pass值：%</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -854,6 +2358,505 @@
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:style val="11"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>手机剩余电量比</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>batt!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>耗电百分比</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:xVal>
+            <c:numRef>
+              <c:f>batt!$A$2:$A$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>49</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>batt!$B$2:$B$61</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>99</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>99</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50040001"/>
+        <c:axId val="50040002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50040001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>次数</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50040002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>电量:%</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -953,6 +2956,41 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>266700</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
@@ -1262,7 +3300,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1270,7 +3308,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1278,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1286,7 +3324,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1294,7 +3332,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1302,7 +3340,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1310,7 +3348,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1318,7 +3356,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1326,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>3</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1334,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1342,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1350,7 +3388,407 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1361,7 +3799,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1369,13 +3807,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1383,13 +3821,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C2">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D2">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1397,13 +3835,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C3">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D3">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1411,13 +3849,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C4">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D4">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1425,13 +3863,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C5">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D5">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1439,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C6">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D6">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1453,13 +3891,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C7">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D7">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1467,13 +3905,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C8">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D8">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1481,13 +3919,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C9">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D9">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1495,13 +3933,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C10">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D10">
-        <v>232056</v>
+        <v>-220786</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1509,13 +3947,713 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="C11">
-        <v>116028</v>
+        <v>-110393</v>
       </c>
       <c r="D11">
-        <v>232056</v>
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-110393</v>
+      </c>
+      <c r="C12">
+        <v>-110393</v>
+      </c>
+      <c r="D12">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>-110393</v>
+      </c>
+      <c r="C13">
+        <v>-110393</v>
+      </c>
+      <c r="D13">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>-110393</v>
+      </c>
+      <c r="C14">
+        <v>-110393</v>
+      </c>
+      <c r="D14">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>-110393</v>
+      </c>
+      <c r="C15">
+        <v>-110393</v>
+      </c>
+      <c r="D15">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>-110393</v>
+      </c>
+      <c r="C16">
+        <v>-110393</v>
+      </c>
+      <c r="D16">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>-110393</v>
+      </c>
+      <c r="C17">
+        <v>-110393</v>
+      </c>
+      <c r="D17">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-110393</v>
+      </c>
+      <c r="C18">
+        <v>-110393</v>
+      </c>
+      <c r="D18">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-110393</v>
+      </c>
+      <c r="C19">
+        <v>-110393</v>
+      </c>
+      <c r="D19">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>-110393</v>
+      </c>
+      <c r="C20">
+        <v>-110393</v>
+      </c>
+      <c r="D20">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-110393</v>
+      </c>
+      <c r="C21">
+        <v>-110393</v>
+      </c>
+      <c r="D21">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>-110393</v>
+      </c>
+      <c r="C22">
+        <v>-110393</v>
+      </c>
+      <c r="D22">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>-110393</v>
+      </c>
+      <c r="C23">
+        <v>-110393</v>
+      </c>
+      <c r="D23">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>-110393</v>
+      </c>
+      <c r="C24">
+        <v>-110393</v>
+      </c>
+      <c r="D24">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>-110393</v>
+      </c>
+      <c r="C25">
+        <v>-110393</v>
+      </c>
+      <c r="D25">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>-110393</v>
+      </c>
+      <c r="C26">
+        <v>-110393</v>
+      </c>
+      <c r="D26">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>-110393</v>
+      </c>
+      <c r="C27">
+        <v>-110393</v>
+      </c>
+      <c r="D27">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>-110393</v>
+      </c>
+      <c r="C28">
+        <v>-110393</v>
+      </c>
+      <c r="D28">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>-110393</v>
+      </c>
+      <c r="C29">
+        <v>-110393</v>
+      </c>
+      <c r="D29">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>-110393</v>
+      </c>
+      <c r="C30">
+        <v>-110393</v>
+      </c>
+      <c r="D30">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>-110393</v>
+      </c>
+      <c r="C31">
+        <v>-110393</v>
+      </c>
+      <c r="D31">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>-110393</v>
+      </c>
+      <c r="C32">
+        <v>-110393</v>
+      </c>
+      <c r="D32">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>-110393</v>
+      </c>
+      <c r="C33">
+        <v>-110393</v>
+      </c>
+      <c r="D33">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>-110393</v>
+      </c>
+      <c r="C34">
+        <v>-110393</v>
+      </c>
+      <c r="D34">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>-110393</v>
+      </c>
+      <c r="C35">
+        <v>-110393</v>
+      </c>
+      <c r="D35">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>-110393</v>
+      </c>
+      <c r="C36">
+        <v>-110393</v>
+      </c>
+      <c r="D36">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>-110393</v>
+      </c>
+      <c r="C37">
+        <v>-110393</v>
+      </c>
+      <c r="D37">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>-110393</v>
+      </c>
+      <c r="C38">
+        <v>-110393</v>
+      </c>
+      <c r="D38">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>-110393</v>
+      </c>
+      <c r="C39">
+        <v>-110393</v>
+      </c>
+      <c r="D39">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>-110393</v>
+      </c>
+      <c r="C40">
+        <v>-110393</v>
+      </c>
+      <c r="D40">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>-110393</v>
+      </c>
+      <c r="C41">
+        <v>-110393</v>
+      </c>
+      <c r="D41">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>-110393</v>
+      </c>
+      <c r="C42">
+        <v>-110393</v>
+      </c>
+      <c r="D42">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>-110393</v>
+      </c>
+      <c r="C43">
+        <v>-110393</v>
+      </c>
+      <c r="D43">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>-110393</v>
+      </c>
+      <c r="C44">
+        <v>-110393</v>
+      </c>
+      <c r="D44">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>-110393</v>
+      </c>
+      <c r="C45">
+        <v>-110393</v>
+      </c>
+      <c r="D45">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>-110393</v>
+      </c>
+      <c r="C46">
+        <v>-110393</v>
+      </c>
+      <c r="D46">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>-110393</v>
+      </c>
+      <c r="C47">
+        <v>-110393</v>
+      </c>
+      <c r="D47">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>-110393</v>
+      </c>
+      <c r="C48">
+        <v>-110393</v>
+      </c>
+      <c r="D48">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>-110393</v>
+      </c>
+      <c r="C49">
+        <v>-110393</v>
+      </c>
+      <c r="D49">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>-110393</v>
+      </c>
+      <c r="C50">
+        <v>-110393</v>
+      </c>
+      <c r="D50">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>-110393</v>
+      </c>
+      <c r="C51">
+        <v>-110393</v>
+      </c>
+      <c r="D51">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>-110393</v>
+      </c>
+      <c r="C52">
+        <v>-110393</v>
+      </c>
+      <c r="D52">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>-110393</v>
+      </c>
+      <c r="C53">
+        <v>-110393</v>
+      </c>
+      <c r="D53">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>-110393</v>
+      </c>
+      <c r="C54">
+        <v>-110393</v>
+      </c>
+      <c r="D54">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>-110393</v>
+      </c>
+      <c r="C55">
+        <v>-110393</v>
+      </c>
+      <c r="D55">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>-110393</v>
+      </c>
+      <c r="C56">
+        <v>-110393</v>
+      </c>
+      <c r="D56">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>-110393</v>
+      </c>
+      <c r="C57">
+        <v>-110393</v>
+      </c>
+      <c r="D57">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>-110393</v>
+      </c>
+      <c r="C58">
+        <v>-110393</v>
+      </c>
+      <c r="D58">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>-110393</v>
+      </c>
+      <c r="C59">
+        <v>-110393</v>
+      </c>
+      <c r="D59">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>-110393</v>
+      </c>
+      <c r="C60">
+        <v>-110393</v>
+      </c>
+      <c r="D60">
+        <v>-220786</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>-110393</v>
+      </c>
+      <c r="C61">
+        <v>-110393</v>
+      </c>
+      <c r="D61">
+        <v>-220786</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +4664,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1534,7 +4672,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1542,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>129</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1550,7 +4688,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>131</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1558,7 +4696,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>131</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1566,7 +4704,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>134</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1574,7 +4712,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>134</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1582,7 +4720,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>134</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1590,7 +4728,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>128</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1598,7 +4736,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>128</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1606,7 +4744,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>128</v>
+        <v>12.1</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1614,7 +4752,906 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>143</v>
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>12.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -330,184 +330,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>163</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>168</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>159</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="3">
+                  <c:v>133</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>71.40000000000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>143</c:v>
                 </c:pt>
-                <c:pt idx="4">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>154</c:v>
-                </c:pt>
                 <c:pt idx="6">
-                  <c:v>162</c:v>
+                  <c:v>113</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>178</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>168</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>162</c:v>
+                  <c:v>117</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>168</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>171</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>159</c:v>
+                  <c:v>126</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>175</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>168</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>168</c:v>
+                  <c:v>143</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>165</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>171</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>175</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>171</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>171</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>168</c:v>
+                  <c:v>134</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>171</c:v>
+                  <c:v>127</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>162</c:v>
+                  <c:v>141</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>156</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>165</c:v>
+                  <c:v>137</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>165</c:v>
+                  <c:v>144</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>165</c:v>
+                  <c:v>75.8</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>162</c:v>
+                  <c:v>114</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>165</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>165</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>165</c:v>
+                  <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>165</c:v>
+                  <c:v>96.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>162</c:v>
+                  <c:v>66.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>181</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="35">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>144</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>151</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>92.8</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>143</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>78.5</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>78.5</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>82.09999999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>60.7</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>78.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>67.8</c:v>
+                </c:pt>
+                <c:pt idx="56">
                   <c:v>153</c:v>
                 </c:pt>
-                <c:pt idx="36">
-                  <c:v>178</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>157</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>175</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>181</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>168</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>159</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>168</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>196</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>165</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>162</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>168</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>171</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>184</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>159</c:v>
-                </c:pt>
                 <c:pt idx="57">
-                  <c:v>171</c:v>
+                  <c:v>82.7</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>171</c:v>
+                  <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>159</c:v>
+                  <c:v>64.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -829,184 +829,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-110393</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-110393</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-110393</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-110393</c:v>
+                  <c:v>367</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-110393</c:v>
+                  <c:v>140</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-110393</c:v>
+                  <c:v>5323</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-110393</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-110393</c:v>
+                  <c:v>525</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-110393</c:v>
+                  <c:v>1558</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-110393</c:v>
+                  <c:v>433</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1222,184 +1222,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-110393</c:v>
+                  <c:v>49</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-110393</c:v>
+                  <c:v>148</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-110393</c:v>
+                  <c:v>538</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-110393</c:v>
+                  <c:v>259</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-110393</c:v>
+                  <c:v>116</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-110393</c:v>
+                  <c:v>1337</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-110393</c:v>
+                  <c:v>197</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-110393</c:v>
+                  <c:v>2960</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-110393</c:v>
+                  <c:v>10711</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-110393</c:v>
+                  <c:v>748</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-110393</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1615,184 +1615,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-220786</c:v>
+                  <c:v>115</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-220786</c:v>
+                  <c:v>288</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>-220786</c:v>
+                  <c:v>538</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>-220786</c:v>
+                  <c:v>94</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>-220786</c:v>
+                  <c:v>626</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>-220786</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>-220786</c:v>
+                  <c:v>6660</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>-220786</c:v>
+                  <c:v>263</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>-220786</c:v>
+                  <c:v>3485</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>-220786</c:v>
+                  <c:v>12269</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>-220786</c:v>
+                  <c:v>1181</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>-220786</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2114,184 +2114,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>12.1</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>12.1</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>12.1</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>12.1</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>12.1</c:v>
+                  <c:v>7.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>12.6</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>12.1</c:v>
+                  <c:v>7.4</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>12.1</c:v>
+                  <c:v>7.5</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>12.1</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>12.1</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>12.2</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>12.2</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>12.2</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>12.1</c:v>
+                  <c:v>7.7</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>12.1</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>12.1</c:v>
+                  <c:v>7.8</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>12.1</c:v>
+                  <c:v>8.9</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>12.1</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>12.1</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>12.1</c:v>
+                  <c:v>8.5</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>12.1</c:v>
+                  <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>12.1</c:v>
+                  <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>12.1</c:v>
+                  <c:v>8.699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>12.1</c:v>
+                  <c:v>9.4</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>12.1</c:v>
+                  <c:v>9.199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>12.1</c:v>
+                  <c:v>8.699999999999999</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>12.1</c:v>
+                  <c:v>8.699999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2613,184 +2613,184 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
                 <c:pt idx="0">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>99</c:v>
+                  <c:v>48</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3316,7 +3316,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>163</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3324,7 +3324,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -3332,7 +3332,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>159</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -3340,7 +3340,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -3348,7 +3348,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>162</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -3356,7 +3356,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>154</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -3364,7 +3364,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>162</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>178</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3380,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>168</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -3388,7 +3388,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>162</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3396,7 +3396,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -3404,7 +3404,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>171</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -3412,7 +3412,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>159</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -3420,7 +3420,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>175</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -3428,7 +3428,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>168</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -3436,7 +3436,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>168</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -3444,7 +3444,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>165</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -3452,7 +3452,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>171</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -3460,7 +3460,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -3468,7 +3468,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>171</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -3476,7 +3476,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>171</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -3484,7 +3484,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>168</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -3492,7 +3492,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>171</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -3500,7 +3500,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -3508,7 +3508,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>156</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -3516,7 +3516,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>165</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -3524,7 +3524,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>165</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -3532,7 +3532,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>165</v>
+        <v>75.8</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -3540,7 +3540,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>162</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -3548,7 +3548,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -3556,7 +3556,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>165</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -3564,7 +3564,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>165</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -3572,7 +3572,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>165</v>
+        <v>96.59999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -3580,7 +3580,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>162</v>
+        <v>66.59999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -3588,7 +3588,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>181</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -3596,7 +3596,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -3604,7 +3604,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>178</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -3612,7 +3612,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>165</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -3620,7 +3620,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -3628,7 +3628,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>175</v>
+        <v>141</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -3636,7 +3636,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>165</v>
+        <v>131</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -3644,7 +3644,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -3652,7 +3652,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -3660,7 +3660,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>175</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -3668,7 +3668,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>181</v>
+        <v>143</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -3676,7 +3676,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>165</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -3684,7 +3684,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -3692,7 +3692,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>168</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -3700,7 +3700,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -3708,7 +3708,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>168</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -3716,7 +3716,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>196</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -3724,7 +3724,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>165</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -3732,7 +3732,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>162</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -3740,7 +3740,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>168</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -3748,7 +3748,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>171</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -3756,7 +3756,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>184</v>
+        <v>67.8</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -3764,7 +3764,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -3772,7 +3772,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>171</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -3780,7 +3780,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>171</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -3788,7 +3788,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>159</v>
+        <v>64.2</v>
       </c>
     </row>
   </sheetData>
@@ -3821,13 +3821,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3835,13 +3835,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-110393</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>-110393</v>
+        <v>49</v>
       </c>
       <c r="D3">
-        <v>-220786</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3849,13 +3849,13 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3863,13 +3863,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3877,13 +3877,13 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3891,13 +3891,13 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>-110393</v>
+        <v>140</v>
       </c>
       <c r="C7">
-        <v>-110393</v>
+        <v>148</v>
       </c>
       <c r="D7">
-        <v>-220786</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3905,13 +3905,13 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3919,13 +3919,13 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3933,13 +3933,13 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3947,13 +3947,13 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3961,13 +3961,13 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>-110393</v>
+        <v>538</v>
       </c>
       <c r="D12">
-        <v>-220786</v>
+        <v>538</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3975,13 +3975,13 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3989,13 +3989,13 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -4003,13 +4003,13 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -4017,13 +4017,13 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -4031,13 +4031,13 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -4045,13 +4045,13 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -4059,13 +4059,13 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -4073,13 +4073,13 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -4087,13 +4087,13 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -4101,13 +4101,13 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -4115,13 +4115,13 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>-110393</v>
+        <v>94</v>
       </c>
       <c r="C23">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>-220786</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -4129,13 +4129,13 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -4143,13 +4143,13 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -4157,13 +4157,13 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -4171,13 +4171,13 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -4185,13 +4185,13 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -4199,13 +4199,13 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>-110393</v>
+        <v>367</v>
       </c>
       <c r="C29">
-        <v>-110393</v>
+        <v>259</v>
       </c>
       <c r="D29">
-        <v>-220786</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -4213,13 +4213,13 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -4227,13 +4227,13 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -4241,13 +4241,13 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -4255,13 +4255,13 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -4269,13 +4269,13 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -4283,13 +4283,13 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -4297,13 +4297,13 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -4311,13 +4311,13 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -4325,13 +4325,13 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -4339,13 +4339,13 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -4353,13 +4353,13 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -4367,13 +4367,13 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -4381,13 +4381,13 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -4395,13 +4395,13 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -4409,13 +4409,13 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -4423,13 +4423,13 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -4437,13 +4437,13 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -4451,13 +4451,13 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>-110393</v>
+        <v>140</v>
       </c>
       <c r="C47">
-        <v>-110393</v>
+        <v>116</v>
       </c>
       <c r="D47">
-        <v>-220786</v>
+        <v>256</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -4465,13 +4465,13 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -4479,13 +4479,13 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -4493,13 +4493,13 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -4507,13 +4507,13 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -4521,13 +4521,13 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>-110393</v>
+        <v>5323</v>
       </c>
       <c r="C52">
-        <v>-110393</v>
+        <v>1337</v>
       </c>
       <c r="D52">
-        <v>-220786</v>
+        <v>6660</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -4535,13 +4535,13 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C53">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -4549,13 +4549,13 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -4563,13 +4563,13 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>-110393</v>
+        <v>66</v>
       </c>
       <c r="C55">
-        <v>-110393</v>
+        <v>197</v>
       </c>
       <c r="D55">
-        <v>-220786</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -4577,13 +4577,13 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C56">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -4591,13 +4591,13 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>-110393</v>
+        <v>525</v>
       </c>
       <c r="C57">
-        <v>-110393</v>
+        <v>2960</v>
       </c>
       <c r="D57">
-        <v>-220786</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -4605,13 +4605,13 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>-110393</v>
+        <v>1558</v>
       </c>
       <c r="C58">
-        <v>-110393</v>
+        <v>10711</v>
       </c>
       <c r="D58">
-        <v>-220786</v>
+        <v>12269</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -4619,13 +4619,13 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C59">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -4633,13 +4633,13 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>-110393</v>
+        <v>433</v>
       </c>
       <c r="C60">
-        <v>-110393</v>
+        <v>748</v>
       </c>
       <c r="D60">
-        <v>-220786</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -4647,13 +4647,13 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="C61">
-        <v>-110393</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>-220786</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4680,7 +4680,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4688,7 +4688,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -4696,7 +4696,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4704,7 +4704,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4712,7 +4712,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>12.1</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4720,7 +4720,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>12.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4728,7 +4728,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4736,7 +4736,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4744,7 +4744,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4752,7 +4752,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4760,7 +4760,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4768,7 +4768,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4776,7 +4776,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4784,7 +4784,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4792,7 +4792,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4800,7 +4800,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4808,7 +4808,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4816,7 +4816,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4824,7 +4824,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4832,7 +4832,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4840,7 +4840,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4848,7 +4848,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4856,7 +4856,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4864,7 +4864,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -4872,7 +4872,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -4880,7 +4880,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -4888,7 +4888,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -4896,7 +4896,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -4904,7 +4904,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4912,7 +4912,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>12.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4920,7 +4920,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4928,7 +4928,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>12.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4936,7 +4936,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>12.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -4944,7 +4944,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>12.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4952,7 +4952,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4960,7 +4960,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4968,7 +4968,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -4976,7 +4976,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -4984,7 +4984,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>12.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -4992,7 +4992,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>12.2</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5000,7 +5000,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5008,7 +5008,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5016,7 +5016,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>12.2</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5024,7 +5024,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5032,7 +5032,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5040,7 +5040,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -5048,7 +5048,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>12.1</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -5056,7 +5056,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>12.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -5064,7 +5064,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>12.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -5072,7 +5072,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>12.1</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -5080,7 +5080,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>12.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -5088,7 +5088,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>12.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -5096,7 +5096,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>12.1</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -5104,7 +5104,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>12.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -5112,7 +5112,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>12.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -5120,7 +5120,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>12.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -5128,7 +5128,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>12.1</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -5136,7 +5136,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>12.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -5144,7 +5144,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>12.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -5152,7 +5152,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>12.1</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -5179,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -5187,7 +5187,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -5195,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -5203,7 +5203,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -5211,7 +5211,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -5219,7 +5219,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -5227,7 +5227,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -5235,7 +5235,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -5243,7 +5243,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -5251,7 +5251,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -5259,7 +5259,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -5267,7 +5267,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -5275,7 +5275,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -5283,7 +5283,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -5291,7 +5291,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -5299,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -5307,7 +5307,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -5315,7 +5315,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -5323,7 +5323,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -5331,7 +5331,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -5339,7 +5339,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -5347,7 +5347,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -5355,7 +5355,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -5363,7 +5363,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -5371,7 +5371,7 @@
         <v>25</v>
       </c>
       <c r="B26">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -5379,7 +5379,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -5387,7 +5387,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -5395,7 +5395,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -5403,7 +5403,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -5411,7 +5411,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -5419,7 +5419,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -5427,7 +5427,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -5435,7 +5435,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -5443,7 +5443,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -5451,7 +5451,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -5459,7 +5459,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -5467,7 +5467,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -5475,7 +5475,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -5483,7 +5483,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -5491,7 +5491,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -5499,7 +5499,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -5507,7 +5507,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -5515,7 +5515,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -5523,7 +5523,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -5531,7 +5531,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -5539,7 +5539,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -5547,7 +5547,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -5555,7 +5555,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -5563,7 +5563,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -5571,7 +5571,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -5579,7 +5579,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -5587,7 +5587,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -5595,7 +5595,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -5603,7 +5603,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -5611,7 +5611,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -5619,7 +5619,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -5627,7 +5627,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -5635,7 +5635,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -5643,7 +5643,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -5651,7 +5651,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>99</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/xlsxReports/cpu_netflow_men_report.xlsx
+++ b/xlsxReports/cpu_netflow_men_report.xlsx
@@ -1,18 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25128"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\javaworkspace\Adb_Monkey_Performance\xlsxReports\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B6FA23-DB00-4EFE-98DF-8506CFBA3084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="cpu" sheetId="1" r:id="rId1"/>
     <sheet name="netflow" sheetId="2" r:id="rId2"/>
-    <sheet name="men" sheetId="3" r:id="rId3"/>
+    <sheet name="mem" sheetId="3" r:id="rId3"/>
     <sheet name="batt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -43,12 +49,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -56,8 +62,15 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -86,17 +99,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -114,12 +144,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -342,7 +374,7 @@
                   <c:v>133</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>71.40000000000001</c:v>
+                  <c:v>71.400000000000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>143</c:v>
@@ -426,10 +458,10 @@
                   <c:v>107</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>96.59999999999999</c:v>
+                  <c:v>96.6</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>66.59999999999999</c:v>
+                  <c:v>66.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="34">
                   <c:v>150</c:v>
@@ -483,7 +515,7 @@
                   <c:v>78.5</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>82.09999999999999</c:v>
+                  <c:v>82.1</c:v>
                 </c:pt>
                 <c:pt idx="52">
                   <c:v>141</c:v>
@@ -512,7 +544,21 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1208-436A-8B07-377865E612F9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50010001"/>
         <c:axId val="50010002"/>
       </c:scatterChart>
@@ -521,6 +567,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -538,9 +585,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010002"/>
         <c:crosses val="autoZero"/>
@@ -551,6 +600,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -569,9 +619,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50010001"/>
         <c:crosses val="autoZero"/>
@@ -580,9 +632,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -593,9 +647,18 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -613,12 +676,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -1011,6 +1076,12 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E2FD-45B9-8AA0-2F17371D699A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1404,6 +1475,12 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E2FD-45B9-8AA0-2F17371D699A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1797,7 +1874,21 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-E2FD-45B9-8AA0-2F17371D699A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50020001"/>
         <c:axId val="50020002"/>
       </c:scatterChart>
@@ -1806,6 +1897,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -1823,9 +1915,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020002"/>
         <c:crosses val="autoZero"/>
@@ -1836,6 +1930,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -1854,9 +1949,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50020001"/>
         <c:crosses val="autoZero"/>
@@ -1865,9 +1962,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -1878,9 +1977,18 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1898,18 +2006,20 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>men!$B$1</c:f>
+              <c:f>mem!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1920,7 +2030,7 @@
           </c:tx>
           <c:xVal>
             <c:numRef>
-              <c:f>men!$A$2:$A$61</c:f>
+              <c:f>mem!$A$2:$A$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
@@ -2109,7 +2219,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>men!$B$2:$B$61</c:f>
+              <c:f>mem!$B$2:$B$61</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="60"/>
@@ -2279,24 +2389,38 @@
                   <c:v>8.6</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>8.699999999999999</c:v>
+                  <c:v>8.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="56">
                   <c:v>9.4</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>9.199999999999999</c:v>
+                  <c:v>9.1999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>8.699999999999999</c:v>
+                  <c:v>8.6999999999999993</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>8.699999999999999</c:v>
+                  <c:v>8.6999999999999993</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B4D8-463A-BA7F-F0A47ED3FCA9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50030001"/>
         <c:axId val="50030002"/>
       </c:scatterChart>
@@ -2305,6 +2429,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -2322,9 +2447,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030002"/>
         <c:crosses val="autoZero"/>
@@ -2335,6 +2462,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -2353,9 +2481,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50030001"/>
         <c:crosses val="autoZero"/>
@@ -2364,9 +2494,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -2377,9 +2509,18 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <c:lang val="en-US"/>
-  <c:style val="11"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="111"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="11"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
   <c:chart>
     <c:title>
       <c:tx>
@@ -2397,12 +2538,14 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
@@ -2795,7 +2938,21 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-517F-4409-A50F-A0D8F5210CF5}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
         <c:axId val="50040001"/>
         <c:axId val="50040002"/>
       </c:scatterChart>
@@ -2804,6 +2961,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -2821,9 +2979,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040002"/>
         <c:crosses val="autoZero"/>
@@ -2834,6 +2994,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -2852,9 +3013,11 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
+          <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="50040001"/>
         <c:crosses val="autoZero"/>
@@ -2863,9 +3026,11 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
+      <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:printSettings>
     <c:headerFooter/>
@@ -2892,7 +3057,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2927,7 +3098,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2962,7 +3139,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -2997,7 +3180,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -3016,7 +3205,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3058,7 +3247,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3090,9 +3279,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -3124,6 +3331,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3299,11 +3524,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3311,7 +3536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3319,7 +3544,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3327,7 +3552,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3335,7 +3560,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3343,15 +3568,15 @@
         <v>133</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>71.40000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>71.400000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3359,7 +3584,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3367,7 +3592,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3375,7 +3600,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3383,7 +3608,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3391,7 +3616,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3399,7 +3624,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3407,7 +3632,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3415,7 +3640,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3423,7 +3648,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3431,7 +3656,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -3439,7 +3664,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -3447,7 +3672,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -3455,7 +3680,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -3463,7 +3688,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -3471,7 +3696,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -3479,7 +3704,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3487,7 +3712,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3495,7 +3720,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3503,7 +3728,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3511,7 +3736,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3519,7 +3744,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3527,7 +3752,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3535,7 +3760,7 @@
         <v>75.8</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3543,7 +3768,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3551,7 +3776,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3559,7 +3784,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3567,23 +3792,23 @@
         <v>107</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34">
-        <v>96.59999999999999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>96.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35">
-        <v>66.59999999999999</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>66.599999999999994</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3591,7 +3816,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3599,7 +3824,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3607,7 +3832,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3615,7 +3840,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3623,7 +3848,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3631,7 +3856,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3639,7 +3864,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3647,7 +3872,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3655,7 +3880,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3663,7 +3888,7 @@
         <v>92.8</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3671,7 +3896,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3679,7 +3904,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3687,7 +3912,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3695,7 +3920,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3703,7 +3928,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3711,7 +3936,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3719,15 +3944,15 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
       <c r="B53">
-        <v>82.09999999999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
+        <v>82.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -3735,7 +3960,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -3743,7 +3968,7 @@
         <v>60.7</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -3751,7 +3976,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -3759,7 +3984,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -3767,7 +3992,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -3775,7 +4000,7 @@
         <v>82.7</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -3783,7 +4008,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -3792,17 +4017,19 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3816,7 +4043,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3830,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -3844,7 +4071,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3858,7 +4085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -3872,7 +4099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -3886,7 +4113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -3900,7 +4127,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -3914,7 +4141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3928,7 +4155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3942,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3956,7 +4183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3970,7 +4197,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3984,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3998,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4012,7 +4239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4026,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4040,7 +4267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4054,7 +4281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4068,7 +4295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4082,7 +4309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4096,7 +4323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4110,7 +4337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4124,7 +4351,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4138,7 +4365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4152,7 +4379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4166,7 +4393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4180,7 +4407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4194,7 +4421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4208,7 +4435,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4222,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4236,7 +4463,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4250,7 +4477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4264,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4278,7 +4505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4292,7 +4519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4306,7 +4533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4320,7 +4547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4334,7 +4561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4348,7 +4575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4362,7 +4589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4376,7 +4603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -4390,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -4404,7 +4631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -4418,7 +4645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -4432,7 +4659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -4446,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -4460,7 +4687,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -4474,7 +4701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -4488,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -4502,7 +4729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -4516,7 +4743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -4530,7 +4757,7 @@
         <v>6660</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -4544,7 +4771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -4558,7 +4785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -4572,7 +4799,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -4586,7 +4813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -4600,7 +4827,7 @@
         <v>3485</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -4614,7 +4841,7 @@
         <v>12269</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -4628,7 +4855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -4642,7 +4869,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -4657,17 +4884,18 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4675,7 +4903,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -4683,7 +4911,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4691,7 +4919,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4699,7 +4927,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4707,7 +4935,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4715,7 +4943,7 @@
         <v>7.6</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -4723,7 +4951,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -4731,7 +4959,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -4739,7 +4967,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -4747,7 +4975,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -4755,7 +4983,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -4763,7 +4991,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -4771,7 +4999,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -4779,7 +5007,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -4787,7 +5015,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -4795,7 +5023,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4803,7 +5031,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4811,7 +5039,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4819,7 +5047,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4827,7 +5055,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4835,7 +5063,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4843,7 +5071,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4851,7 +5079,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4859,7 +5087,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4867,7 +5095,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -4875,7 +5103,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -4883,7 +5111,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -4891,7 +5119,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -4899,7 +5127,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -4907,7 +5135,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -4915,7 +5143,7 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -4923,7 +5151,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -4931,7 +5159,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -4939,7 +5167,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -4947,7 +5175,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -4955,7 +5183,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -4963,7 +5191,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -4971,7 +5199,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -4979,7 +5207,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -4987,7 +5215,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -4995,7 +5223,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5003,7 +5231,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5011,7 +5239,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5019,7 +5247,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5027,7 +5255,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5035,7 +5263,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5043,7 +5271,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5051,7 +5279,7 @@
         <v>7.7</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5059,7 +5287,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5067,7 +5295,7 @@
         <v>7.8</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5075,7 +5303,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5083,7 +5311,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5091,7 +5319,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5099,7 +5327,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5107,7 +5335,7 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5115,15 +5343,15 @@
         <v>8.6</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
       <c r="B57">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5131,42 +5359,43 @@
         <v>9.4</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
       <c r="B59">
-        <v>9.199999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
       <c r="B60">
-        <v>8.699999999999999</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
       <c r="B61">
-        <v>8.699999999999999</v>
+        <v>8.6999999999999993</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5174,7 +5403,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
@@ -5182,7 +5411,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>2</v>
       </c>
@@ -5190,7 +5419,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>3</v>
       </c>
@@ -5198,7 +5427,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>4</v>
       </c>
@@ -5206,7 +5435,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>5</v>
       </c>
@@ -5214,7 +5443,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>6</v>
       </c>
@@ -5222,7 +5451,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>7</v>
       </c>
@@ -5230,7 +5459,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>8</v>
       </c>
@@ -5238,7 +5467,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>9</v>
       </c>
@@ -5246,7 +5475,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>10</v>
       </c>
@@ -5254,7 +5483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>11</v>
       </c>
@@ -5262,7 +5491,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>12</v>
       </c>
@@ -5270,7 +5499,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>13</v>
       </c>
@@ -5278,7 +5507,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>14</v>
       </c>
@@ -5286,7 +5515,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>15</v>
       </c>
@@ -5294,7 +5523,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>16</v>
       </c>
@@ -5302,7 +5531,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>17</v>
       </c>
@@ -5310,7 +5539,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>18</v>
       </c>
@@ -5318,7 +5547,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>19</v>
       </c>
@@ -5326,7 +5555,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>20</v>
       </c>
@@ -5334,7 +5563,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22">
         <v>21</v>
       </c>
@@ -5342,7 +5571,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23">
         <v>22</v>
       </c>
@@ -5350,7 +5579,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24">
         <v>23</v>
       </c>
@@ -5358,7 +5587,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25">
         <v>24</v>
       </c>
@@ -5366,7 +5595,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5374,7 +5603,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5382,7 +5611,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5390,7 +5619,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5398,7 +5627,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5406,7 +5635,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5414,7 +5643,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5422,7 +5651,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5430,7 +5659,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5438,7 +5667,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A35">
         <v>34</v>
       </c>
@@ -5446,7 +5675,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A36">
         <v>35</v>
       </c>
@@ -5454,7 +5683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A37">
         <v>36</v>
       </c>
@@ -5462,7 +5691,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A38">
         <v>37</v>
       </c>
@@ -5470,7 +5699,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A39">
         <v>38</v>
       </c>
@@ -5478,7 +5707,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A40">
         <v>39</v>
       </c>
@@ -5486,7 +5715,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A41">
         <v>40</v>
       </c>
@@ -5494,7 +5723,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A42">
         <v>41</v>
       </c>
@@ -5502,7 +5731,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A43">
         <v>42</v>
       </c>
@@ -5510,7 +5739,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A44">
         <v>43</v>
       </c>
@@ -5518,7 +5747,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A45">
         <v>44</v>
       </c>
@@ -5526,7 +5755,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A46">
         <v>45</v>
       </c>
@@ -5534,7 +5763,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A47">
         <v>46</v>
       </c>
@@ -5542,7 +5771,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A48">
         <v>47</v>
       </c>
@@ -5550,7 +5779,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A49">
         <v>48</v>
       </c>
@@ -5558,7 +5787,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A50">
         <v>49</v>
       </c>
@@ -5566,7 +5795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A51">
         <v>50</v>
       </c>
@@ -5574,7 +5803,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A52">
         <v>51</v>
       </c>
@@ -5582,7 +5811,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A53">
         <v>52</v>
       </c>
@@ -5590,7 +5819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A54">
         <v>53</v>
       </c>
@@ -5598,7 +5827,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A55">
         <v>54</v>
       </c>
@@ -5606,7 +5835,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A56">
         <v>55</v>
       </c>
@@ -5614,7 +5843,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A57">
         <v>56</v>
       </c>
@@ -5622,7 +5851,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A58">
         <v>57</v>
       </c>
@@ -5630,7 +5859,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A59">
         <v>58</v>
       </c>
@@ -5638,7 +5867,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A60">
         <v>59</v>
       </c>
@@ -5646,7 +5875,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A61">
         <v>60</v>
       </c>
@@ -5655,6 +5884,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
